--- a/output_excel/17176228.xlsx
+++ b/output_excel/17176228.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C6500"/>
     </font>
   </fonts>
   <fills count="5">
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,27 +563,19 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>P1-11 | CONEX. | (DCIM) | (DCIM) | (DCIM) | (DCIM) | ANCORAR | ANCORAR | BF-A | BF-A | V1-2 | 1x2x4AC | 30K | 33.59M | BT | 30K | 30K | 3x336AN | 112,5KVA | 31.69M | MT | 112,5KVA | 3x336AN | 1x3x120(70)AX | 112,5KVA | 3x336AN | 37,5KVA | 37,5KVA | CAMPO | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | 37,5KVA | 1x2x4AC | BT | 112,5KVA | 112,5KVA | BT | AVENIDA | (DCIM) | CONEX. | 112,5KVA | 112,5KVA | 112,5KVA | 30K | CONEX. | CABOS | 3x336AN | 3x70AX(5AZN) | BF-A | C12X1000112,5KVACE2 | (DCIM) | FONTE | 30K | 400816F | P2 | CAMPO | 30K</t>
+          <t>CONEX. | (DCIM) | (DCIM) | (DCIM) | (DCIM) | ANCORAR | ANCORAR | BF-A | BF-A | 4 | 3 | 33.59M | BT | 3 | 3 | 6 | 1 | 31.69M | MT</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -616,13 +608,13 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>P2 | 38.80M | 38.80M | V2-3 | BT | (DCIM) | 30K | MT | 400816F | 1x3x120(70)AX | 1x3x120(70)AX | BF-A | 30K | V1-2 | 3x185AX(5AZN) | CEAFC4112,5KVAIP | 112,5KVA | 1AF(1) | 3x185AX(5AZN) | AVENIDA | BT | CONEX. | (DCIM) | 112,5KVA | BT | 30K | MT | 30K | 1x2x4AC | 3x336AN | CONEX. | (DCIM) | 112,5KVA | 112,5KVA | (DCIM) | 112,5KVA | 112,5KVA | (KL) | (DCIM) | 112,5KVA | (DCIM) | CAMPO | RESUMO | (DCIM) | BIF | N°: | B1F | 112,5KVA | (DCIM) | CABOS | 400816F | (DCIM) | 112,5KVA | 112,5KVA | CABOS | (DCIM) | 112,5KVA | CABOS | ANCORAR | CONEX. | (DCIM) | N°: | ESTR. | 112,5KVA | (DCIM) | CABOS | (DCIM) | 30K | CAMPO | 112,5KVA | CAMPO | (DCIM) | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
+          <t>1x3x120(70)AX | 38.80M | BF-A | 8 | 0 | 0 | 1 | (DCIM) | BT | CONEX. | BT | 3x185AX(5AZN) | 4 | 38.80M | MT | 112,5KVA | (DCIM) | 0 | 0 | AVENIDA | 6 | 1AF(1) | CONEX. | 2 | CEAFC4112,5KVAIP | 1</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -665,13 +657,13 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P6 | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | 112,5KVA | 112,5KVA | 37,5KVA | AVENIDA | 37,5KVA | SEM | 112,5KVA | .8 | 37,5KVA | 3x336AN | 1x2x4AC | BT | (DCIM) | (DCIM) | 112,5KVA | 3x336AN | Z | 37,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 3x336AN | 3x185AX(5AZN) | PASSEIO | 3x336AN | CAMPO | CONEX. | 112,5KVA | 3x336AN | .8 | (DCIM) | 37,5KVA | P7X | 1x2x4AC | 112,5KVA | 38M | 112,5KVA | CONEX. | 112,5KVA | 112,5KVA | 37,5KVA | 1x3x120(70)AX | 37,5KVA | V7-8 | BF-A | 30K | 400816F | 112,5KVA | 1x3x120(70)AX | 112,5KVA | 112,5KVA | 112,5KVA | 30K | CONEX. | 112,5KVA | 30K | BF-A | 30K | 112,5KVA | BF-A | MT | CONEX. | 28.93M | BT | 30K | ANCORAR | ANCORAR | 3x185AX(5AZN) | CONEX. | (DCIM) | TX10 | 112,5KVA | (DCIM) | (DCIM) | SMDT112,5KVAL1(1) | BT | C12X1000112,5KVACEAFC4112,5KVACE3112,5KVAIP | BT | 28.93M | 112,5KVA | (DCIM) | (DCIM) | 1x3x120(70)AX | B1F | 3x336AN</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+          <t>C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | SEM | 1 | 1 | 7 | AVENIDA | 7</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -702,27 +694,19 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>P9 | (DCIM) | 112,5KVA | 112,5KVA | CONEX. | C09x600,L1(2),IP | FT | 30K112,5KVACE3 | P7X | (DCIM) | ETAPA | (DCIM) | (DCIM) | BF-A | ANCORAR | 112,5KVA | BT | 37,5KVA | 17176296 | CONEX. | 112,5KVA | P8 | 3x336AN | (DCIM) | TV. | B1F | (DCIM) | 37,5KVA | 30K | BF-A | ANCORAR | 17176297 | 112,5KVA | 112,5KVA | (DCIM) | DOS | (KL) | 37,5KVA | CONEX. | 37,5KVA | B1F | 112,5KVA | 112,5KVA | 3x336AN | 112,5KVA | 112,5KVA | BCU | 112,5KVA | 37,5KVA | 27.90M | 112,5KVA | GUIA | (DCIM) | 30K | 400816F | 112,5KVA | 37,5KVA | 28 | 3x336AN | 112,5KVA | 112,5KVA | 112,5KVA | ANCORAR | 112,5KVA | CAMPO | ANCORAR | 30K | 112,5KVA | 112,5KVA | BT | PASSEIO | CABOS | 28.38M | 112,5KVA | (DCIM) | AVENIDA | SMFL112,5KVAL1(1) | CONEX.</t>
+          <t>(DCIM) | 1 | 2 | CONEX. | 60 | FT | 0112,5KVACE3 | P7X | (DCIM) | (DCIM) | (DCIM) | ETAPA | BF-A | ANCORAR | BT | 2 | 7 | B1F | TV. | 2 | (DCIM) | 17176296 | 6 | CONEX. | (DCIM) | 3 | BF-A | ANCORAR | 7 | DOS | (DCIM) | (KL) | 1 | B1F | 1 | CONEX. | 7 | 17176297 | 112,5KVA | 112,5KVA | 7 | 2 | 1RU6A | 6 | 1 | 1 | GUIA | 7 | (DCIM) | 1 | 3 | 8 | 3x336AN | 2 | 1 | 7 | 27.90M | ANCORAR | 28 | ANCORAR | 112,5KVA | 1 | 5 | 3 | CAMPO | CABOS | 112,5KVA | 112,5KVA | 1 | BT | (DCIM) | AVENIDA | PASSEIO | 4 | CONEX. | 28.38M | 112,5KVA</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -752,20 +736,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31.69m</t>
+          <t>38.80m</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>V1-2 | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | CONEX. | P1-11 | (DCIM) | P2 | 1x2x4AC | (DCIM) | BT | (DCIM) | CONEX. | (DCIM) | 112,5KVA | 31.69M | 38.80M | 30K | ANCORAR | RESUMO | ANCORAR | (DCIM) | BF-A | 112,5KVA | BF-A | 112,5KVA | 400816F | 38.80M | BF-A | CONEX. | 30K | 3x336AN | ANCORAR | 30K | 33.59M | (DCIM) | 1x2x4AC | 112,5KVA | 30K | 30K | 112,5KVA | (DCIM) | CABOS | (DCIM) | 30K | (DCIM) | 30K | ANCORAR | 3x336AN | CAMPO | 112,5KVA | AVENIDA | 112,5KVA | (DCIM) | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | (KL) | 1AF(1) | (DCIM) | CABOS | 112,5KVA | 3x336AN | 112,5KVA | (DCIM) | 3x336AN | 112,5KVA | CLANDESTINOS:</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
+          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 38.80M | 38.80M</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -797,20 +781,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33.42m</t>
+          <t>38.80m</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V2-3 | BT | 3x185AX(5AZN) | MT | 33.42M | 33.42M | CAMPO | 38.80M | 38.80M | 30K | P2 | AVENIDA | BT | 112,5KVA | CAMPO | 112,5KVA | 112,5KVA | 175ET005296879 | 30K | 112,5KVA | 37,5KVA | 3x336AN | 400816F | 112,5KVA | 112,5KVA | 112,5KVA | V3-4 | BT | 37,5KVA | N°: | 17176228 | MT | BF-A | (DCIM) | 112,5KVA | BIF | CONEX. | INSTALAÇÃO | 112,5KVA | 30K | 30K | 112,5KVA | B1F | N°: | 30K | (DCIM) | 112,5KVA | (DCIM) | BF-A | 1x3x120(70)AX | AVENIDA | CABOS | DESATIVAÇÃO | (DCIM) | 112,5KVA | 3x185AX(5AZN) | CABOS | ESTR. | (DCIM) | BT | 112,5KVA | FERRAGEM | 112,5KVA | 112,5KVA | (KL)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
+          <t>BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | 38.80M | 38.80M | (DCIM)</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -842,20 +826,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19.85m</t>
+          <t>33.42m</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V3-4 | BT | 3x185AX(5AZN) | MT | CAMPO | 1x2x4AC | 19.85M | 33.42M | 33.42M | 19.85M | 30K | CAMPO | CABOS | ESTR. | CLANDESTINOS: | 30K | 3x336AN | 30K | CONEX. | LOCAL | 112,5KVA | 30K | (DCIM) | 112,5KVA | AVENIDA | (DCIM) | 30K | 1AF(1) | PARTICULA | INSTALAÇÃO | COMPARTILHANTES | 112,5KVAIP | 112,5KVA | BF-A | 112,5KVA | 37,5KVA | FERRAGEM | BT | 112,5KVA | V4-5 | DESATIVAÇÃO | (DCIM) | BT | CABOS | 1x3x120(70)AX | 112,5KVA | 112,5KVA | CAMPO</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
+          <t>3 | CAMPO | CAMPO | 4 | BT | 1x3x120(70)AX | (DCIM) | 1 | 0 | CONEX. | 6 | 33.42M | 112,5KVA | 0 | MT | 0 | 1 | 112,5KVA | 3x185AX(5AZN) | (DCIM) | AVENIDA | CABOS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -887,20 +871,20 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19.85m</t>
+          <t>45.25m</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | 19.85M | 19.85M | CAMPO | COMPARTILHANTES | 175ET005296879 | 45.25M | 112,5KVA | ANCORAR | PARTICULA | 45.25M | CONEX. | LOCAL | CABOS | ESTR. | CLANDESTINOS: | 7115 | BM | 1x2x4AC | 112,5KVA | CAMPO | 30K | BT | CONEX. | 112,5KVA | 30K | 1x3x120(70)AX | 3x185AX(5AZN) | BF-A | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
+          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 45.25M | 175ET005296879 | CAMPO | 45.25M | 5 | CONEX.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
@@ -927,7 +911,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -943,13 +927,13 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P10 | AVENIDA | BT | 112,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | CAMPO | 37,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 3x336AN | 37,5KVA | 112,5KVA | 3x336AN | 30K | 112,5KVA | 112,5KVA | 112,5KVA | 572059 | 112,5KVA | TX10 | 400816F | 37,5KVA | C12X300112,5KVACEAFC1112,5KVAIP | ANCORAR | 30K | BF-A | AV. | 112,5KVA | BF-A | ANCORAR | CABOS | P8 | ANCORAR | SMFL112,5KVAL1(1) | CABOS | (DCIM) | BF-A | 36.70M | (DCIM) | ANCORAR | CONEX. | 79M | (DCIM) | (DCIM) | (DCIM) | 17176297 | GUIA | CALÇADA | 17176296 | CAMINHÃO | BF-A | ANCORAR | 28.38M | ODD | GA | ETAPA | 27.90M | BF-A | ANCORAR | ODI | 28 | 1x2x4AC | 112,5KVA | 112,5KVA | (DCIM) | 30K</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+          <t>CONEX. | ETAPA | 17176296 | 17176297 | FT | SMFL112,5KVAL1(1) | 28 | C12X300112,5KVACEAFC1112,5KVAIP | BF-A | BF-A</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
@@ -971,32 +955,36 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VAO</t>
+          <t>POSTE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>V6-7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38m</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>P8</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V6-7 | BT | 3x185AX(5AZN) | MT | BF-A | 38M | TX10 | 28.93M | 112,5KVA | 28.93M | C12X1000112,5KVACEAFC4112,5KVACE3112,5KVAIP | SMDT112,5KVAL1(1) | 45.25M | 7115 | P6 | SEM | 45.25M | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | MT | V7-8 | BT</t>
+          <t>ODD | ODI | BF-A | BF-A | 79M | BF-A | 28 | SMFL112,5KVAL1(1) | TX10 | C12X300112,5KVACEAFC1112,5KVAIP</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>CRITICO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1021,30 +1009,124 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>V7-8</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28.38m</t>
+          <t>28.93m</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3x185AX(5AZN) | V7-8 | MT | 1x3x120(70)AX | PASSEIO | BT | SEM | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | 28.38M | 27.90M | MT | 3x70AX(5AZN) | P7X | (KL) | 112,5KVA | (DCIM) | ANCORAR | 28.93M | 28.93M | (DCIM) | 112,5KVA | B1F | ANCORAR | (DCIM) | BCU | GA | 112,5KVA | 30K | 112,5KVA | 1x2x4AC | 36.70M | P6 | P9 | FT</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
+          <t>28.93M | 28.93M | 1x3x120(70)AX | 3x185AX(5AZN) | BT | MT | 38M | BF-A</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>17176228</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>VAO</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>V7-8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28.38m</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) | MT | 1x3x120(70)AX | PASSEIO | BT | SEM | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | 28.38M | 27.90M | MT | 3x70AX(5AZN) | P7X</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>17176228</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>POSTE</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>P10 | 1 | 1 | AVENIDA | 36.70M | CONEX. | 7 | 7 | BT | 1 | 3 | 1 | C12X300112,5KVACEAFC1112,5KVAIP | 112,5KVA | 7 | 7 | SMFL112,5KVAL1(1) | TX10 | 27.90M | CAMPO | 1RU6A | 28.38M | 6 | 6 | 17176297 | 112,5KVA | AV. | 2 | 2</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>

--- a/output_excel/17176228.xlsx
+++ b/output_excel/17176228.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="5">
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -565,20 +583,31 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | (DCIM) | (DCIM) | (DCIM) | (DCIM) | ANCORAR | ANCORAR | BF-A | BF-A | 4 | 3 | 33.59M | BT | 3 | 3 | 6 | 1 | 31.69M | MT</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SMFL112,5KVAL1(2) C12X1000112,5KVACE2112,5KVA(DCIM) | P1-11 | 2 CS's (DCIM) CAMPO (DCIM)112,5KVA(KL) 1 (DCIM) 2 (DCIM) | BT V1-2 1x3x120(70)AX | MT 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -606,20 +635,31 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1x3x120(70)AX | 38.80M | BF-A | 8 | 0 | 0 | 1 | (DCIM) | BT | CONEX. | BT | 3x185AX(5AZN) | 4 | 38.80M | MT | 112,5KVA | (DCIM) | 0 | 0 | AVENIDA | 6 | 1AF(1) | CONEX. | 2 | CEAFC4112,5KVAIP | 1</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SMFL112,5KVAL1(2) C12X1000112,5KVACE2112,5KVA(DCIM) | 2 CS's (DCIM) CAMPO (DCIM)112,5KVA(KL) 1 (DCIM) 2 (DCIM) | P2 | BT V1-2 1x3x120(70)AX | MT 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -645,30 +685,33 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | SEM | 1 | 1 | 7 | AVENIDA | 7</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7115 C12X1000112,5KVACEAFC4112,5KVACE3112,5KVAIP SMDT112,5KVAL1(1) | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | P6 | (DCIM) 1 2 CONEX. 60 0112,5KVACE3 | SEM PASSEIO | 1 1 7 1 7 | P7X</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -696,20 +739,31 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | 1 | 2 | CONEX. | 60 | FT | 0112,5KVACE3 | P7X | (DCIM) | (DCIM) | (DCIM) | ETAPA | BF-A | ANCORAR | BT | 2 | 7 | B1F | TV. | 2 | (DCIM) | 17176296 | 6 | CONEX. | (DCIM) | 3 | BF-A | ANCORAR | 7 | DOS | (DCIM) | (KL) | 1 | B1F | 1 | CONEX. | 7 | 17176297 | 112,5KVA | 112,5KVA | 7 | 2 | 1RU6A | 6 | 1 | 1 | GUIA | 7 | (DCIM) | 1 | 3 | 8 | 3x336AN | 2 | 1 | 7 | 27.90M | ANCORAR | 28 | ANCORAR | 112,5KVA | 1 | 5 | 3 | CAMPO | CABOS | 112,5KVA | 112,5KVA | 1 | BT | (DCIM) | AVENIDA | PASSEIO | 4 | CONEX. | 28.38M | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10m</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>(DCIM) 1 2 CONEX. 60 0112,5KVACE3 | P9 | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | C12X300112,5KVACEAFC1112,5KVAIP | xP8 SMFL112,5KVAL1(1) | FT ETAPA | P7X | TV. DOS B1F</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -734,27 +788,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>38.80m</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 38.80M | 38.80M</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+          <t>31.69m</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MT 3x185AX(5AZN) | 4 BT CONEX. 1 0 2 V1-3 8 0 (DCIM) | 38.80M MT | RESUMO 1RU6A 112,5KVA (DCIM) 112,5KVA (DCIM) 2 CS's B1F BIF N°: 2 8 | 38.80M V2-3 BT 1x3x120(70)AX | 1RU6A CLANDESTINOS: 112,5KVA (DCIM) 112,5KVA (DCIM) 2 CS's ESTR. (DCIM) N°: 1 | 2 CS's (DCIM) CAMPO (DCIM)112,5KVA(KL) 1 (DCIM) 2 (DCIM) | 31.69M</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -779,27 +836,30 @@
           <t>V2-3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38.80m</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | 38.80M | 38.80M | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
+          <t>38.80m</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>38.80M V2-3 BT 1x3x120(70)AX | 38.80M MT | 3x185AX(5AZN) 33.42M 33.42M MT | 4 BT CONEX. 1 0 2 V1-3 8 0 (DCIM) | 2 CS's (DCIM) CAMPO (DCIM)112,5KVA(KL) 1 (DCIM) 2 (DCIM) | MT 3x185AX(5AZN) | RESUMO 1RU6A 112,5KVA (DCIM) 112,5KVA (DCIM) 2 CS's B1F BIF N°: 2 8 | 1RU6A CLANDESTINOS: 112,5KVA (DCIM) 112,5KVA (DCIM) 2 CS's ESTR. (DCIM) N°: 1</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -824,27 +884,30 @@
           <t>V3-4</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33.42m</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3 | CAMPO | CAMPO | 4 | BT | 1x3x120(70)AX | (DCIM) | 1 | 0 | CONEX. | 6 | 33.42M | 112,5KVA | 0 | MT | 0 | 1 | 112,5KVA | 3x185AX(5AZN) | (DCIM) | AVENIDA | CABOS</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
+          <t>33.42m</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) 33.42M 33.42M MT | 3x185AX(5AZN) 19.85M 19.85M | 2 BT CONEX. 1 0 2 V1-3 2 8 (DCIM) | 38.80M V2-3 BT 1x3x120(70)AX | 38.80M MT | BT MT 1x3x120(70)AX 3x185AX(5AZN) | 1 3 BT CONEX. 1 0 2 V1-3 5 3 5 (DCIM)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -869,27 +932,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>45.25m</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x185AX(5AZN) | MT | 45.25M | 175ET005296879 | CAMPO | 45.25M | 5 | CONEX.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+          <t>45.25m</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>BT MT 1x3x120(70)AX 3x185AX(5AZN) | 45.25M 45.25M | 3x185AX(5AZN) 19.85M 19.85M | 1 3 BT CONEX. 1 0 2 V1-3 5 3 5 (DCIM) | xBM | CABOS CLANDESTINOS: LOCAL COMPARTILHANTES | 2 TX10 2 V1-3 38M</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -911,34 +977,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>CONEX. | ETAPA | 17176296 | 17176297 | FT | SMFL112,5KVAL1(1) | 28 | C12X300112,5KVACEAFC1112,5KVAIP | BF-A | BF-A</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACEAFC1112,5KVAIP | xP8 SMFL112,5KVAL1(1) | 17176296 28 2 V1-3 ODI | (DCIM) 1 2 CONEX. 60 0112,5KVACE3 | CONEX. 17176297 2 V1-3 ODD | P10 572059 | (DCIM) BT 3 CONEX. 1 8 5 112,5KVA CONEX. 3x185AX(5AZN) 112,5KVA 1x3x70(70)AXNI(5AZN) | FT ETAPA</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -955,39 +1024,38 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>POSTE</t>
+          <t>VAO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>V6-7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>ODD | ODI | BF-A | BF-A | 79M | BF-A | 28 | SMFL112,5KVAL1(1) | TX10 | C12X300112,5KVACEAFC1112,5KVAIP</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
+          <t>28.93m</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) 28.93M 28.93M | 2 TX10 2 V1-3 38M | MT V7-8 3x185AX(5AZN) | MT | MT 3x70AX(5AZN) | SEM PASSEIO | 45.25M 45.25M | 28.38M 27.90M</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1009,124 +1077,33 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>V6-7</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28.93m</t>
-        </is>
-      </c>
+          <t>V7-8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28.93M | 28.93M | 1x3x120(70)AX | 3x185AX(5AZN) | BT | MT | 38M | BF-A</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+          <t>36.70m</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>MT V7-8 3x185AX(5AZN) | 28.38M 27.90M | MT 3x70AX(5AZN) | SEM PASSEIO | 36.70M | 3x185AX(5AZN) 28.93M 28.93M | 2 TX10 2 V1-3 38M | xP8 SMFL112,5KVAL1(1)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17176228</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>VAO</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>V7-8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28.38m</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3x185AX(5AZN) | MT | 1x3x120(70)AX | PASSEIO | BT | SEM | C10X300112,5KVACE2112,5KVASMTG112,5KVAIP | 28.38M | 27.90M | MT | 3x70AX(5AZN) | P7X</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17176228</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>POSTE</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>P10 | 1 | 1 | AVENIDA | 36.70M | CONEX. | 7 | 7 | BT | 1 | 3 | 1 | C12X300112,5KVACEAFC1112,5KVAIP | 112,5KVA | 7 | 7 | SMFL112,5KVAL1(1) | TX10 | 27.90M | CAMPO | 1RU6A | 28.38M | 6 | 6 | 17176297 | 112,5KVA | AV. | 2 | 2</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
